--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260629.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260629.xlsx
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>66,234,553</t>
+          <t>138,208,467</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>138,208,467</t>
+          <t>66,234,553</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>38,510,370</t>
+          <t>22,595,320</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>22,595,320</t>
+          <t>38,510,370</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
